--- a/九龙-红磡-首汇/首汇_销控明细表.xlsx
+++ b/九龙-红磡-首汇/首汇_销控明细表.xlsx
@@ -789,7 +789,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -851,7 +851,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7209,7 +7209,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8643,7 +8643,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10201,7 +10201,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10511,7 +10511,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10635,7 +10635,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10759,7 +10759,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10883,7 +10883,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10945,7 +10945,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11263,7 +11263,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11325,7 +11325,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11449,7 +11449,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11573,7 +11573,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11767,7 +11767,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11953,7 +11953,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -12077,7 +12077,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12263,7 +12263,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12519,7 +12519,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12581,7 +12581,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12643,7 +12643,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12705,7 +12705,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12829,7 +12829,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12891,7 +12891,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12953,7 +12953,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -13015,7 +13015,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -13077,7 +13077,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -13139,7 +13139,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13201,7 +13201,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13263,7 +13263,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13511,7 +13511,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13697,7 +13697,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13829,7 +13829,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13953,7 +13953,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -14015,7 +14015,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -14077,7 +14077,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -14139,7 +14139,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14201,7 +14201,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14263,7 +14263,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14325,7 +14325,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14449,7 +14449,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14573,7 +14573,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14697,7 +14697,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14759,7 +14759,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14821,7 +14821,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14883,7 +14883,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -15007,7 +15007,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -15069,7 +15069,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15263,7 +15263,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15325,7 +15325,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15457,7 +15457,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15713,7 +15713,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -15775,7 +15775,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15837,7 +15837,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -16044,7 +16044,7 @@
           <t>A | 850呎 (4+房)
 $2982万
 $35,082/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -16108,7 +16108,7 @@
           <t>J | 348呎 (2房)
 $829万
 $23,819/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="K5" s="20" t="inlineStr">
@@ -16116,7 +16116,7 @@
           <t>K | 356呎 (2房)
 $790万
 $22,181/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="L5" s="22" t="inlineStr"/>
@@ -16148,7 +16148,7 @@
           <t>C | 531呎 (3房)
 $1369万
 $25,774/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -16156,7 +16156,7 @@
           <t>D | 406呎 (2房)
 $1002万
 $24,677/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -16164,7 +16164,7 @@
           <t>E | 408呎 (2房)
 $972万
 $23,817/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -16172,7 +16172,7 @@
           <t>F | 266呎 (1房)
 $639万
 $24,026/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -16180,7 +16180,7 @@
           <t>G | 274呎 (1房)
 $672万
 $24,520/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -16188,7 +16188,7 @@
           <t>H | 265呎 (1房)
 $574万
 $21,668/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -16196,7 +16196,7 @@
           <t>J | 347呎 (2房)
 $717万
 $20,653/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -16204,7 +16204,7 @@
           <t>K | 348呎 (2房)
 $730万
 $20,974/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="L6" s="20" t="inlineStr">
@@ -16212,7 +16212,7 @@
           <t>L | 356呎 (2房)
 $775万
 $21,773/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -16227,7 +16227,7 @@
           <t>A | 600呎 (4+房)
 $1630万
 $27,167/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -16235,7 +16235,7 @@
           <t>B | 534呎 (3房)
 $1226万
 $22,952/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -16243,7 +16243,7 @@
           <t>C | 531呎 (3房)
 $1310万
 $24,663/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -16251,7 +16251,7 @@
           <t>D | 406呎 (2房)
 $1024万
 $25,215/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -16259,7 +16259,7 @@
           <t>E | 408呎 (2房)
 $961万
 $23,550/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -16267,7 +16267,7 @@
           <t>F | 266呎 (1房)
 $632万
 $23,755/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -16275,7 +16275,7 @@
           <t>G | 274呎 (1房)
 $664万
 $24,241/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -16283,7 +16283,7 @@
           <t>H | 265呎 (1房)
 $588万
 $22,204/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -16291,7 +16291,7 @@
           <t>J | 347呎 (2房)
 $710万
 $20,474/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
@@ -16299,7 +16299,7 @@
           <t>K | 348呎 (2房)
 $724万
 $20,793/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="L7" s="20" t="inlineStr">
@@ -16307,7 +16307,7 @@
           <t>L | 356呎 (2房)
 $773万
 $21,703/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
     </row>
@@ -16322,7 +16322,7 @@
           <t>A | 600呎 (4+房)
 $1628万
 $27,133/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -16330,7 +16330,7 @@
           <t>B | 534呎 (3房)
 $1219万
 $22,822/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -16338,7 +16338,7 @@
           <t>C | 531呎 (3房)
 $1302万
 $24,522/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -16346,7 +16346,7 @@
           <t>D | 406呎 (2房)
 $1018万
 $25,073/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="F8" s="24" t="inlineStr">
@@ -16362,7 +16362,7 @@
           <t>F | 266呎 (1房)
 $628万
 $23,623/呎
-(26年-03月-27日)</t>
+(26年-03月-28日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -16370,7 +16370,7 @@
           <t>G | 274呎 (1房)
 $660万
 $24,103/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -16378,7 +16378,7 @@
           <t>H | 265呎 (1房)
 $568万
 $21,427/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -16386,7 +16386,7 @@
           <t>J | 347呎 (2房)
 $708万
 $20,417/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr">
@@ -16394,7 +16394,7 @@
           <t>K | 348呎 (2房)
 $722万
 $20,734/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="L8" s="20" t="inlineStr">
@@ -16402,7 +16402,7 @@
           <t>L | 356呎 (2房)
 $783万
 $21,996/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -16425,7 +16425,7 @@
           <t>B | 534呎 (3房)
 $1207万
 $22,596/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -16433,7 +16433,7 @@
           <t>C | 531呎 (3房)
 $1289万
 $24,276/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -16441,7 +16441,7 @@
           <t>D | 406呎 (2房)
 $975万
 $24,023/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -16449,7 +16449,7 @@
           <t>E | 408呎 (2房)
 $946万
 $23,184/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -16457,7 +16457,7 @@
           <t>F | 266呎 (1房)
 $622万
 $23,386/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -16465,7 +16465,7 @@
           <t>G | 274呎 (1房)
 $654万
 $23,857/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -16473,7 +16473,7 @@
           <t>H | 265呎 (1房)
 $563万
 $21,247/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -16481,7 +16481,7 @@
           <t>J | 347呎 (2房)
 $702万
 $20,238/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr">
@@ -16489,7 +16489,7 @@
           <t>K | 348呎 (2房)
 $739万
 $21,235/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="L9" s="20" t="inlineStr">
@@ -16497,7 +16497,7 @@
           <t>L | 356呎 (2房)
 $751万
 $21,099/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
     </row>
@@ -16520,7 +16520,7 @@
           <t>B | 534呎 (3房)
 $1200万
 $22,468/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -16528,7 +16528,7 @@
           <t>C | 531呎 (3房)
 $1282万
 $24,136/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -16536,7 +16536,7 @@
           <t>D | 406呎 (2房)
 $921万
 $22,682/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -16544,7 +16544,7 @@
           <t>E | 408呎 (2房)
 $940万
 $23,051/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -16552,7 +16552,7 @@
           <t>F | 266呎 (1房)
 $639万
 $24,026/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -16560,7 +16560,7 @@
           <t>G | 274呎 (1房)
 $650万
 $23,715/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -16568,7 +16568,7 @@
           <t>H | 265呎 (1房)
 $560万
 $21,128/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -16576,7 +16576,7 @@
           <t>J | 347呎 (2房)
 $698万
 $20,119/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="K10" s="25" t="inlineStr">
@@ -16592,7 +16592,7 @@
           <t>L | 356呎 (2房)
 $755万
 $21,206/呎
-(26年-04月-06日)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
     </row>
@@ -16615,7 +16615,7 @@
           <t>B | 534呎 (3房)
 $1249万
 $23,390/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -16623,7 +16623,7 @@
           <t>C | 531呎 (3房)
 $1267万
 $23,856/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -16631,7 +16631,7 @@
           <t>D | 406呎 (2房)
 $910万
 $22,422/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -16639,7 +16639,7 @@
           <t>E | 408呎 (2房)
 $955万
 $23,398/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -16647,7 +16647,7 @@
           <t>F | 266呎 (1房)
 $611万
 $22,984/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -16655,7 +16655,7 @@
           <t>G | 274呎 (1房)
 $682万
 $24,885/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -16663,7 +16663,7 @@
           <t>H | 265呎 (1房)
 $557万
 $21,009/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -16671,7 +16671,7 @@
           <t>J | 347呎 (2房)
 $731万
 $21,063/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -16679,7 +16679,7 @@
           <t>K | 348呎 (2房)
 $779万
 $22,389/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="L11" s="20" t="inlineStr">
@@ -16687,7 +16687,7 @@
           <t>L | 356呎 (2房)
 $742万
 $20,849/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
     </row>
@@ -16710,7 +16710,7 @@
           <t>B | 534呎 (3房)
 $1236万
 $23,152/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -16718,7 +16718,7 @@
           <t>C | 531呎 (3房)
 $1254万
 $23,610/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -16726,7 +16726,7 @@
           <t>D | 406呎 (2房)
 $901万
 $22,192/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -16734,7 +16734,7 @@
           <t>E | 408呎 (2房)
 $945万
 $23,157/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -16742,7 +16742,7 @@
           <t>F | 266呎 (1房)
 $605万
 $22,747/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -16750,7 +16750,7 @@
           <t>G | 274呎 (1房)
 $635万
 $23,193/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -16758,7 +16758,7 @@
           <t>H | 265呎 (1房)
 $554万
 $20,887/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -16766,7 +16766,7 @@
           <t>J | 347呎 (2房)
 $727万
 $20,939/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -16774,7 +16774,7 @@
           <t>K | 348呎 (2房)
 $721万
 $20,728/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="L12" s="20" t="inlineStr">
@@ -16782,7 +16782,7 @@
           <t>L | 356呎 (2房)
 $738万
 $20,725/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
     </row>
@@ -16797,7 +16797,7 @@
           <t>A | 600呎 (4+房)
 $1585万
 $26,417/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -16805,7 +16805,7 @@
           <t>B | 534呎 (3房)
 $1229万
 $23,017/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -16813,7 +16813,7 @@
           <t>C | 531呎 (3房)
 $1179万
 $22,210/呎
-(26年-03月-27日)</t>
+(26年-03月-28日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -16821,7 +16821,7 @@
           <t>D | 406呎 (2房)
 $896万
 $22,061/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -16829,7 +16829,7 @@
           <t>E | 408呎 (2房)
 $939万
 $23,021/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -16837,7 +16837,7 @@
           <t>F | 266呎 (1房)
 $602万
 $22,632/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -16845,7 +16845,7 @@
           <t>G | 274呎 (1房)
 $671万
 $24,474/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -16853,7 +16853,7 @@
           <t>H | 265呎 (1房)
 $550万
 $20,768/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -16861,7 +16861,7 @@
           <t>J | 347呎 (2房)
 $722万
 $20,812/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -16869,7 +16869,7 @@
           <t>K | 348呎 (2房)
 $729万
 $20,948/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="L13" s="20" t="inlineStr">
@@ -16877,7 +16877,7 @@
           <t>L | 356呎 (2房)
 $733万
 $20,601/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -16892,7 +16892,7 @@
           <t>A | 600呎 (4+房)
 $1555万
 $25,912/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -16900,7 +16900,7 @@
           <t>B | 534呎 (3房)
 $1236万
 $23,137/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -16908,7 +16908,7 @@
           <t>C | 531呎 (3房)
 $1192万
 $22,446/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -16916,10 +16916,105 @@
           <t>D | 406呎 (2房)
 $890万
 $21,933/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$934万
+$22,884/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$600万
+$22,544/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$678万
+$24,731/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$549万
+$20,710/呎
+(26年-04月-21日)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$694万
+$20,005/呎
+(26年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="K14" s="20" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$715万
+$20,542/呎
 (26年-04月-22日)</t>
         </is>
       </c>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="L14" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$731万
+$20,538/呎
+(26年-04月-28日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1257万
+$23,547/呎
+(26年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1172万
+$22,078/呎
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$938万
+$23,096/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 408呎 (2房)
 $934万
@@ -16927,62 +17022,157 @@
 (26年-04月-22日)</t>
         </is>
       </c>
-      <c r="G14" s="20" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
 $600万
 $22,544/呎
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$667万
+$24,326/呎
 (26年-04月-23日)</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$678万
-$24,731/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="I14" s="20" t="inlineStr">
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>H | 265呎 (1房)
-$549万
-$20,710/呎
+$589万
+$22,211/呎
 (26年-04月-20日)</t>
         </is>
       </c>
-      <c r="J14" s="20" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>J | 347呎 (2房)
 $694万
 $20,005/呎
-(26年-04月-19日)</t>
-        </is>
-      </c>
-      <c r="K14" s="20" t="inlineStr">
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="K15" s="20" t="inlineStr">
         <is>
           <t>K | 348呎 (2房)
 $715万
 $20,542/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="L14" s="20" t="inlineStr">
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="L15" s="20" t="inlineStr">
         <is>
           <t>L | 356呎 (2房)
 $731万
 $20,538/呎
+(26年-04月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+$1551万
+$25,848/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1147万
+$21,472/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1158万
+$21,814/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$880万
+$21,671/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$908万
+$22,264/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$613万
+$23,035/呎
 (26年-04月-27日)</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$658万
+$24,031/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$552万
+$20,832/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$686万
+$19,766/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="K16" s="20" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$688万
+$19,761/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="L16" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$722万
+$20,290/呎
+(26年-05月-04日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 600呎 (4+房)
 招标单位
@@ -16990,189 +17180,189 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 534呎 (3房)
-$1257万
-$23,547/呎
-(26年-04月-28日)</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="inlineStr">
+$1143万
+$21,408/呎
+(26年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 531呎 (3房)
-$1172万
-$22,078/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="E15" s="20" t="inlineStr">
+$1155万
+$21,747/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 406呎 (2房)
-$938万
-$23,096/呎
+$875万
+$21,540/呎
 (26年-04月-23日)</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 408呎 (2房)
-$934万
-$22,884/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="G15" s="20" t="inlineStr">
+$893万
+$21,887/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
-$600万
-$22,544/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="H15" s="20" t="inlineStr">
+$609万
+$22,892/呎
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 274呎 (1房)
-$667万
-$24,326/呎
+$616万
+$22,497/呎
 (26年-04月-22日)</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>H | 265呎 (1房)
-$589万
-$22,211/呎
-(26年-04月-19日)</t>
-        </is>
-      </c>
-      <c r="J15" s="20" t="inlineStr">
+$550万
+$20,769/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>J | 347呎 (2房)
-$694万
-$20,005/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="K15" s="20" t="inlineStr">
+$684万
+$19,704/呎
+(26年-04月-16日)</t>
+        </is>
+      </c>
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>K | 348呎 (2房)
-$715万
-$20,542/呎
+$708万
+$20,358/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$725万
+$20,355/呎
+(26年-05月-04日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+$1515万
+$25,250/呎
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1136万
+$21,280/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1179万
+$22,195/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$867万
+$21,345/呎
 (26年-04月-23日)</t>
         </is>
       </c>
-      <c r="L15" s="20" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$885万
+$21,686/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$624万
+$23,442/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$617万
+$22,534/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$531万
+$20,041/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$682万
+$19,644/呎
+(26年-04月-16日)</t>
+        </is>
+      </c>
+      <c r="K18" s="20" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$706万
+$20,294/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="L18" s="20" t="inlineStr">
         <is>
           <t>L | 356呎 (2房)
-$731万
-$20,538/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-$1551万
-$25,848/呎
-(26年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1147万
-$21,472/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1158万
-$21,814/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$880万
-$21,671/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="F16" s="20" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$908万
-$22,264/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="G16" s="20" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$613万
-$23,035/呎
-(26年-04月-26日)</t>
-        </is>
-      </c>
-      <c r="H16" s="20" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$658万
-$24,031/呎
-(26年-05月-10日)</t>
-        </is>
-      </c>
-      <c r="I16" s="20" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$552万
-$20,832/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="J16" s="20" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$686万
-$19,766/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="K16" s="20" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$688万
-$19,761/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="L16" s="20" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$722万
-$20,290/呎
-(26年-05月-03日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
+$718万
+$20,179/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 600呎 (4+房)
 招标单位
@@ -17180,189 +17370,94 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 534呎 (3房)
-$1143万
-$21,408/呎
-(26年-04月-19日)</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
+$1176万
+$22,023/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 531呎 (3房)
-$1155万
-$21,747/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="inlineStr">
+$1168万
+$21,992/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 406呎 (2房)
-$875万
-$21,540/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="F17" s="20" t="inlineStr">
+$851万
+$20,955/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 408呎 (2房)
-$893万
-$21,887/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="G17" s="20" t="inlineStr">
+$868万
+$21,287/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
-$609万
-$22,892/呎
-(26年-04月-26日)</t>
-        </is>
-      </c>
-      <c r="H17" s="20" t="inlineStr">
+$592万
+$22,267/呎
+(26年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 274呎 (1房)
-$616万
-$22,497/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="I17" s="20" t="inlineStr">
+$599万
+$21,869/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>H | 265呎 (1房)
-$550万
-$20,769/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="J17" s="20" t="inlineStr">
+$529万
+$19,980/呎
+(26年-04月-16日)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
         <is>
           <t>J | 347呎 (2房)
-$684万
-$19,704/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="K17" s="20" t="inlineStr">
+$680万
+$19,608/呎
+(26年-04月-16日)</t>
+        </is>
+      </c>
+      <c r="K19" s="20" t="inlineStr">
         <is>
           <t>K | 348呎 (2房)
-$708万
-$20,358/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="L17" s="20" t="inlineStr">
+$681万
+$19,580/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="L19" s="20" t="inlineStr">
         <is>
           <t>L | 356呎 (2房)
-$725万
-$20,355/呎
-(26年-05月-03日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-$1515万
-$25,250/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1136万
-$21,280/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="D18" s="20" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1179万
-$22,195/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$867万
-$21,345/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="F18" s="20" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$885万
-$21,686/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="G18" s="20" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$624万
-$23,442/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="H18" s="20" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$617万
-$22,534/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="I18" s="20" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$531万
-$20,041/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="J18" s="20" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$682万
-$19,644/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="K18" s="20" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$706万
-$20,294/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="L18" s="20" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$718万
-$20,179/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
+$716万
+$20,119/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 600呎 (4+房)
 招标单位
@@ -17370,94 +17465,94 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 534呎 (3房)
-$1176万
-$22,023/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="D19" s="20" t="inlineStr">
+$1123万
+$21,022/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 531呎 (3房)
-$1168万
-$21,992/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="inlineStr">
+$1164万
+$21,922/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 406呎 (2房)
-$851万
-$20,955/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="F19" s="20" t="inlineStr">
+$845万
+$20,824/呎
+(26年-04月-21日)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 408呎 (2房)
-$868万
-$21,287/呎
+$863万
+$21,154/呎
+(26年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$589万
+$22,124/呎
+(26年-04月-21日)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$595万
+$21,728/呎
+(26年-04月-21日)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$528万
+$19,922/呎
+(26年-04月-16日)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$703万
+$20,246/呎
 (26年-04月-22日)</t>
         </is>
       </c>
-      <c r="G19" s="20" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$592万
-$22,267/呎
-(26年-04月-19日)</t>
-        </is>
-      </c>
-      <c r="H19" s="20" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$599万
-$21,869/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="I19" s="20" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$529万
-$19,980/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="J19" s="20" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$680万
-$19,608/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="K19" s="20" t="inlineStr">
+      <c r="K20" s="20" t="inlineStr">
         <is>
           <t>K | 348呎 (2房)
-$681万
-$19,580/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="L19" s="20" t="inlineStr">
+$679万
+$19,521/呎
+(26年-04月-17日)</t>
+        </is>
+      </c>
+      <c r="L20" s="20" t="inlineStr">
         <is>
           <t>L | 356呎 (2房)
-$716万
-$20,119/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B20" s="21" t="inlineStr">
+$714万
+$20,055/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 600呎 (4+房)
 招标单位
@@ -17465,94 +17560,189 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 534呎 (3房)
-$1123万
-$21,022/呎
+$1119万
+$20,958/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1160万
+$21,854/呎
 (26年-04月-23日)</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$840万
+$20,693/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$872万
+$21,372/呎
+(26年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$604万
+$22,718/呎
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$592万
+$21,590/呎
+(26年-04月-21日)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$532万
+$20,082/呎
+(26年-04月-28日)</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$665万
+$19,170/呎
+(26年-04月-16日)</t>
+        </is>
+      </c>
+      <c r="K21" s="20" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$677万
+$19,459/呎
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="L21" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$712万
+$19,995/呎
+(26年-04月-27日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+$1488万
+$24,800/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1116万
+$20,894/呎
+(26年-04月-21日)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 531呎 (3房)
-$1164万
-$21,922/呎
+$1163万
+$21,907/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$835万
+$20,563/呎
 (26年-04月-23日)</t>
         </is>
       </c>
-      <c r="E20" s="20" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$845万
-$20,824/呎
-(26年-04月-20日)</t>
-        </is>
-      </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 408呎 (2房)
-$863万
-$21,154/呎
-(26年-04月-19日)</t>
-        </is>
-      </c>
-      <c r="G20" s="20" t="inlineStr">
+$852万
+$20,888/呎
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
-$589万
-$22,124/呎
-(26年-04月-20日)</t>
-        </is>
-      </c>
-      <c r="H20" s="20" t="inlineStr">
+$581万
+$21,847/呎
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 274呎 (1房)
-$595万
-$21,728/呎
-(26年-04月-20日)</t>
-        </is>
-      </c>
-      <c r="I20" s="20" t="inlineStr">
+$591万
+$21,568/呎
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>H | 265呎 (1房)
-$528万
-$19,922/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="J20" s="20" t="inlineStr">
+$548万
+$20,683/呎
+(26年-04月-16日)</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
         <is>
           <t>J | 347呎 (2房)
-$703万
-$20,246/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="K20" s="20" t="inlineStr">
+$663万
+$19,113/呎
+(26年-04月-16日)</t>
+        </is>
+      </c>
+      <c r="K22" s="20" t="inlineStr">
         <is>
           <t>K | 348呎 (2房)
-$679万
-$19,521/呎
-(26年-04月-16日)</t>
-        </is>
-      </c>
-      <c r="L20" s="20" t="inlineStr">
+$675万
+$19,399/呎
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="L22" s="20" t="inlineStr">
         <is>
           <t>L | 356呎 (2房)
-$714万
-$20,055/呎
+$717万
+$20,153/呎
 (26年-04月-23日)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B21" s="21" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 600呎 (4+房)
 招标单位
@@ -17560,118 +17750,23 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 534呎 (3房)
-$1119万
-$20,958/呎
+$1153万
+$21,590/呎
 (26年-04月-23日)</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 531呎 (3房)
-$1160万
-$21,854/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="E21" s="20" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$840万
-$20,693/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$872万
-$21,372/呎
-(26年-04月-19日)</t>
-        </is>
-      </c>
-      <c r="G21" s="20" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$604万
-$22,718/呎
-(26年-04月-26日)</t>
-        </is>
-      </c>
-      <c r="H21" s="20" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$592万
-$21,590/呎
-(26年-04月-20日)</t>
-        </is>
-      </c>
-      <c r="I21" s="20" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$532万
-$20,082/呎
+$1157万
+$21,786/呎
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="J21" s="20" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$665万
-$19,170/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="K21" s="20" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$677万
-$19,459/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="L21" s="20" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$712万
-$19,995/呎
-(26年-04月-26日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-$1488万
-$24,800/呎
-(26年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1116万
-$20,894/呎
-(26年-04月-20日)</t>
-        </is>
-      </c>
-      <c r="D22" s="20" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1163万
-$21,907/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 406呎 (2房)
 $835万
@@ -17679,70 +17774,165 @@
 (26年-04月-22日)</t>
         </is>
       </c>
-      <c r="F22" s="20" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 408呎 (2房)
 $852万
 $20,888/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="G22" s="20" t="inlineStr">
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 266呎 (1房)
 $581万
 $21,847/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="H22" s="20" t="inlineStr">
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 274呎 (1房)
-$591万
-$21,568/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="I22" s="20" t="inlineStr">
+$597万
+$21,806/呎
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>H | 265呎 (1房)
-$548万
-$20,683/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="J22" s="20" t="inlineStr">
+$525万
+$19,803/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
         <is>
           <t>J | 347呎 (2房)
 $663万
 $19,113/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="K22" s="20" t="inlineStr">
+(26年-04月-16日)</t>
+        </is>
+      </c>
+      <c r="K23" s="20" t="inlineStr">
         <is>
           <t>K | 348呎 (2房)
 $675万
 $19,399/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="L22" s="20" t="inlineStr">
+(26年-04月-17日)</t>
+        </is>
+      </c>
+      <c r="L23" s="20" t="inlineStr">
         <is>
           <t>L | 356呎 (2房)
-$717万
-$20,153/呎
+$710万
+$19,931/呎
 (26年-04月-22日)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 600呎 (4+房)
+$1478万
+$24,633/呎
+(26年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 534呎 (3房)
+$1109万
+$20,766/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 531呎 (3房)
+$1183万
+$22,280/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 406呎 (2房)
+$824万
+$20,303/呎
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 408呎 (2房)
+$869万
+$21,310/呎
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 266呎 (1房)
+$574万
+$21,566/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>G | 274呎 (1房)
+$580万
+$21,170/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>H | 265呎 (1房)
+$523万
+$19,746/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t>J | 347呎 (2房)
+$659万
+$18,993/呎
+(26年-04月-16日)</t>
+        </is>
+      </c>
+      <c r="K24" s="20" t="inlineStr">
+        <is>
+          <t>K | 348呎 (2房)
+$671万
+$19,278/呎
+(26年-04月-17日)</t>
+        </is>
+      </c>
+      <c r="L24" s="20" t="inlineStr">
+        <is>
+          <t>L | 356呎 (2房)
+$705万
+$19,808/呎
+(26年-05月-04日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 600呎 (4+房)
 招标单位
@@ -17750,202 +17940,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1153万
-$21,590/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1157万
-$21,786/呎
-(26年-04月-26日)</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$835万
-$20,563/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="F23" s="20" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$852万
-$20,888/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="G23" s="20" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$581万
-$21,847/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="H23" s="20" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$597万
-$21,806/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="I23" s="20" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$525万
-$19,803/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="J23" s="20" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$663万
-$19,113/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="K23" s="20" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$675万
-$19,399/呎
-(26年-04月-16日)</t>
-        </is>
-      </c>
-      <c r="L23" s="20" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$710万
-$19,931/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-$1478万
-$24,633/呎
-(26年-04月-28日)</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>B | 534呎 (3房)
-$1109万
-$20,766/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>C | 531呎 (3房)
-$1183万
-$22,280/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
-        <is>
-          <t>D | 406呎 (2房)
-$824万
-$20,303/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="F24" s="20" t="inlineStr">
-        <is>
-          <t>E | 408呎 (2房)
-$869万
-$21,310/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="G24" s="20" t="inlineStr">
-        <is>
-          <t>F | 266呎 (1房)
-$574万
-$21,566/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="H24" s="20" t="inlineStr">
-        <is>
-          <t>G | 274呎 (1房)
-$580万
-$21,170/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="I24" s="20" t="inlineStr">
-        <is>
-          <t>H | 265呎 (1房)
-$523万
-$19,746/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="J24" s="20" t="inlineStr">
-        <is>
-          <t>J | 347呎 (2房)
-$659万
-$18,993/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="K24" s="20" t="inlineStr">
-        <is>
-          <t>K | 348呎 (2房)
-$671万
-$19,278/呎
-(26年-04月-16日)</t>
-        </is>
-      </c>
-      <c r="L24" s="20" t="inlineStr">
-        <is>
-          <t>L | 356呎 (2房)
-$705万
-$19,808/呎
-(26年-05月-03日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B25" s="21" t="inlineStr">
-        <is>
-          <t>A | 600呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 534呎 (3房)
 $1105万
 $20,702/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -17953,7 +17953,7 @@
           <t>C | 531呎 (3房)
 $1179万
 $22,210/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -17961,7 +17961,7 @@
           <t>D | 406呎 (2房)
 $819万
 $20,172/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -17969,7 +17969,7 @@
           <t>E | 408呎 (2房)
 $836万
 $20,488/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -17977,7 +17977,7 @@
           <t>F | 266呎 (1房)
 $570万
 $21,424/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -17985,7 +17985,7 @@
           <t>G | 274呎 (1房)
 $576万
 $21,028/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -17993,7 +17993,7 @@
           <t>H | 265呎 (1房)
 $523万
 $19,729/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -18001,7 +18001,7 @@
           <t>J | 347呎 (2房)
 $655万
 $18,882/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="K25" s="20" t="inlineStr">
@@ -18009,7 +18009,7 @@
           <t>K | 348呎 (2房)
 $666万
 $19,148/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="L25" s="20" t="inlineStr">
@@ -18017,7 +18017,7 @@
           <t>L | 356呎 (2房)
 $701万
 $19,681/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -18032,7 +18032,7 @@
           <t>A | 560呎 (4+房)
 $1608万
 $28,714/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -18040,7 +18040,7 @@
           <t>B | 498呎 (3房)
 $1285万
 $25,800/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -18048,7 +18048,7 @@
           <t>C | 493呎 (3房)
 $1267万
 $25,700/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -18056,7 +18056,7 @@
           <t>D | 369呎 (2房)
 $948万
 $25,700/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -18064,7 +18064,7 @@
           <t>E | 370呎 (2房)
 $940万
 $25,400/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -18080,7 +18080,7 @@
           <t>G | 236呎 (1房)
 $642万
 $27,200/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -18096,7 +18096,7 @@
           <t>J | 309呎 (2房)
 $791万
 $25,600/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="K26" s="20" t="inlineStr">
@@ -18104,7 +18104,7 @@
           <t>K | 310呎 (2房)
 $784万
 $25,300/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="L26" s="20" t="inlineStr">
@@ -18112,7 +18112,7 @@
           <t>L | 319呎 (2房)
 $740万
 $23,200/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
     </row>

--- a/九龙-红磡-首汇/首汇_销控明细表.xlsx
+++ b/九龙-红磡-首汇/首汇_销控明细表.xlsx
@@ -9630,38 +9630,30 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H144" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I144" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H144" s="5" t="n">
+        <v>15230000</v>
+      </c>
+      <c r="I144" s="5" t="n">
+        <v>25383</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K144" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L144" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K144" s="5" t="n">
+        <v>15230000</v>
+      </c>
+      <c r="L144" s="5" t="n">
+        <v>25383</v>
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
@@ -9670,7 +9662,7 @@
       </c>
       <c r="N144" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -15947,7 +15939,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -15957,7 +15949,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>218</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -17172,12 +17164,12 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 600呎 (4+房)
-招标单位
--
-(在售)</t>
+$1523万
+$25,383/呎
+(26年-08月-19日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">

--- a/九龙-红磡-首汇/首汇_销控明细表.xlsx
+++ b/九龙-红磡-首汇/首汇_销控明细表.xlsx
@@ -9635,7 +9635,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -17169,7 +17169,7 @@
           <t>A | 600呎 (4+房)
 $1523万
 $25,383/呎
-(26年-08月-19日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
